--- a/packages/kotlin/ttr-report-cli/src/test/resources/worlds/reports/model/reports/returns_review_q/template.xlsx
+++ b/packages/kotlin/ttr-report-cli/src/test/resources/worlds/reports/model/reports/returns_review_q/template.xlsx
@@ -43,7 +43,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.###############"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11.0"/>
@@ -83,10 +85,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
+      <alignment wrapText="true"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -131,9 +148,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="0">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/packages/kotlin/ttr-report-cli/src/test/resources/worlds/reports/model/reports/returns_review_q/template.xlsx
+++ b/packages/kotlin/ttr-report-cli/src/test/resources/worlds/reports/model/reports/returns_review_q/template.xlsx
@@ -44,7 +44,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.###############"/>
+    <numFmt numFmtId="164" formatCode="0.0##############"/>
   </numFmts>
   <fonts count="3">
     <font>
